--- a/content_forms/043_marketing_collaboration_brief_request_form--content_forms.xlsx
+++ b/content_forms/043_marketing_collaboration_brief_request_form--content_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -763,7 +763,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Marketing Collaboration Brief Request Form Agency</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Marketing Collaboration Brief Request Form Client</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Creator</t>
+          <t>Marketing Collaboration Brief Request Form Creator</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
